--- a/www/terminologies/ValueSet-JDV-J210-SpecialiteOrdinale-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J210-SpecialiteOrdinale-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="237">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260730120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,37 +120,25 @@
     <t>SI01</t>
   </si>
   <si>
-    <t>Exercice infirmier en pratique avancée pathologies chroniques stabilisées (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Pathologies chroniques stabilisées (SI)</t>
   </si>
   <si>
     <t>SI02</t>
   </si>
   <si>
-    <t>Exercice infirmier en pratique avancée oncologie et hémato-oncologie (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Oncologie et hémato-oncologie (SI)</t>
   </si>
   <si>
     <t>SI03</t>
   </si>
   <si>
-    <t>Exercice infirmier en pratique avancée maladie rénale chronique, dialyse et transplantation rénale (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Maladie rénale chronique, dialyse, transplantation rénale (SI)</t>
   </si>
   <si>
     <t>SI04</t>
   </si>
   <si>
-    <t>Exercice infirmier en pratique avancée santé mentale (SI)</t>
-  </si>
-  <si>
-    <t>SI06</t>
-  </si>
-  <si>
-    <t>Infirmier(ère) de bloc opératoire (SI)</t>
-  </si>
-  <si>
-    <t>SI07</t>
-  </si>
-  <si>
-    <t>Infirmier(ère) anesthésiste (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Psychiatrie et santé mentale (SI)</t>
   </si>
   <si>
     <t>SI08</t>
@@ -997,7 +985,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1841,31 +1829,15 @@
         <v>234</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B106" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>240</v>
       </c>
     </row>
   </sheetData>
